--- a/authorization_forms/029_device_access_agreement--authorization_forms.xlsx
+++ b/authorization_forms/029_device_access_agreement--authorization_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -738,8 +738,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -767,12 +767,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'laptop'}</t>
+          <t>laptop</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Laptop'}</t>
+          <t>Laptop</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'smartphone'}</t>
+          <t>smartphone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Smartphone'}</t>
+          <t>Smartphone</t>
         </is>
       </c>
     </row>
@@ -801,12 +801,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'tablet'}</t>
+          <t>tablet</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Tablet'}</t>
+          <t>Tablet</t>
         </is>
       </c>
     </row>
@@ -818,12 +818,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'read',_'value':_'read'}</t>
+          <t>read</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Read', 'value': 'Read'}</t>
+          <t>Read</t>
         </is>
       </c>
     </row>
@@ -835,12 +835,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'write',_'value':_'write'}</t>
+          <t>write</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Write', 'value': 'Write'}</t>
+          <t>Write</t>
         </is>
       </c>
     </row>
@@ -852,12 +852,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'admin',_'value':_'admin'}</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Admin', 'value': 'Admin'}</t>
+          <t>Admin</t>
         </is>
       </c>
     </row>
